--- a/docs/downloads/24092026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/24092026Tduh Developer Project Sales Status 13.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BP18"/>
+  <dimension ref="A2:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,9 @@
     <col width="9" customWidth="1" min="66" max="66"/>
     <col width="9" customWidth="1" min="67" max="67"/>
     <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -634,8 +637,11 @@
       <c r="BK3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BN3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="BQ3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -967,17 +973,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BN4" s="6" t="inlineStr">
+      <c r="BN4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BO4" s="6" t="inlineStr">
+      <c r="BO4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BP4" s="6" t="inlineStr">
+      <c r="BP4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BQ4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BR4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BS4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1104,15 +1125,26 @@
         <f>BL5/$D$5</f>
         <v/>
       </c>
-      <c r="BN5" s="12">
+      <c r="BN5" s="10">
         <f>BO5-BL5</f>
         <v/>
       </c>
-      <c r="BO5" s="12" t="n">
+      <c r="BO5" s="10" t="n">
         <v>214</v>
       </c>
-      <c r="BP5" s="13">
+      <c r="BP5" s="11">
         <f>BO5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BQ5" s="12">
+        <f>BR5-BO5</f>
+        <v/>
+      </c>
+      <c r="BR5" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="BS5" s="13">
+        <f>BR5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1357,15 +1389,26 @@
         <f>BL6/$D$6</f>
         <v/>
       </c>
-      <c r="BN6" s="12">
+      <c r="BN6" s="10">
         <f>BO6-BL6</f>
         <v/>
       </c>
-      <c r="BO6" s="12" t="n">
+      <c r="BO6" s="10" t="n">
         <v>392</v>
       </c>
-      <c r="BP6" s="13">
+      <c r="BP6" s="11">
         <f>BO6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BQ6" s="12">
+        <f>BR6-BO6</f>
+        <v/>
+      </c>
+      <c r="BR6" s="12" t="n">
+        <v>402</v>
+      </c>
+      <c r="BS6" s="13">
+        <f>BR6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1453,9 +1496,12 @@
       <c r="BK7" s="10" t="n"/>
       <c r="BL7" s="10" t="n"/>
       <c r="BM7" s="11" t="n"/>
-      <c r="BN7" s="12" t="n"/>
-      <c r="BO7" s="12" t="n"/>
-      <c r="BP7" s="13" t="n"/>
+      <c r="BN7" s="10" t="n"/>
+      <c r="BO7" s="10" t="n"/>
+      <c r="BP7" s="11" t="n"/>
+      <c r="BQ7" s="12" t="n"/>
+      <c r="BR7" s="12" t="n"/>
+      <c r="BS7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1698,15 +1744,26 @@
         <f>BL8/$D$8</f>
         <v/>
       </c>
-      <c r="BN8" s="12">
+      <c r="BN8" s="10">
         <f>BO8-BL8</f>
         <v/>
       </c>
-      <c r="BO8" s="12" t="n">
+      <c r="BO8" s="10" t="n">
         <v>1028</v>
       </c>
-      <c r="BP8" s="13">
+      <c r="BP8" s="11">
         <f>BO8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BQ8" s="12">
+        <f>BR8-BO8</f>
+        <v/>
+      </c>
+      <c r="BR8" s="12" t="n">
+        <v>1039</v>
+      </c>
+      <c r="BS8" s="13">
+        <f>BR8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -1951,15 +2008,26 @@
         <f>BL9/$D$9</f>
         <v/>
       </c>
-      <c r="BN9" s="12">
+      <c r="BN9" s="10">
         <f>BO9-BL9</f>
         <v/>
       </c>
-      <c r="BO9" s="12" t="n">
+      <c r="BO9" s="10" t="n">
         <v>1132</v>
       </c>
-      <c r="BP9" s="13">
+      <c r="BP9" s="11">
         <f>BO9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BQ9" s="12">
+        <f>BR9-BO9</f>
+        <v/>
+      </c>
+      <c r="BR9" s="12" t="n">
+        <v>1132</v>
+      </c>
+      <c r="BS9" s="13">
+        <f>BR9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2204,15 +2272,26 @@
         <f>BL10/$D$10</f>
         <v/>
       </c>
-      <c r="BN10" s="12">
+      <c r="BN10" s="10">
         <f>BO10-BL10</f>
         <v/>
       </c>
-      <c r="BO10" s="12" t="n">
+      <c r="BO10" s="10" t="n">
         <v>530</v>
       </c>
-      <c r="BP10" s="13">
+      <c r="BP10" s="11">
         <f>BO10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BQ10" s="12">
+        <f>BR10-BO10</f>
+        <v/>
+      </c>
+      <c r="BR10" s="12" t="n">
+        <v>535</v>
+      </c>
+      <c r="BS10" s="13">
+        <f>BR10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2457,15 +2536,26 @@
         <f>BL11/$D$11</f>
         <v/>
       </c>
-      <c r="BN11" s="12">
+      <c r="BN11" s="10">
         <f>BO11-BL11</f>
         <v/>
       </c>
-      <c r="BO11" s="12" t="n">
+      <c r="BO11" s="10" t="n">
         <v>470</v>
       </c>
-      <c r="BP11" s="13">
+      <c r="BP11" s="11">
         <f>BO11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BQ11" s="12">
+        <f>BR11-BO11</f>
+        <v/>
+      </c>
+      <c r="BR11" s="12" t="n">
+        <v>470</v>
+      </c>
+      <c r="BS11" s="13">
+        <f>BR11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2710,15 +2800,26 @@
         <f>BL12/$D$12</f>
         <v/>
       </c>
-      <c r="BN12" s="12">
+      <c r="BN12" s="10">
         <f>BO12-BL12</f>
         <v/>
       </c>
-      <c r="BO12" s="12" t="n">
+      <c r="BO12" s="10" t="n">
         <v>238</v>
       </c>
-      <c r="BP12" s="13">
+      <c r="BP12" s="11">
         <f>BO12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BQ12" s="12">
+        <f>BR12-BO12</f>
+        <v/>
+      </c>
+      <c r="BR12" s="12" t="n">
+        <v>239</v>
+      </c>
+      <c r="BS12" s="13">
+        <f>BR12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -2963,15 +3064,26 @@
         <f>BL13/$D$13</f>
         <v/>
       </c>
-      <c r="BN13" s="12">
+      <c r="BN13" s="10">
         <f>BO13-BL13</f>
         <v/>
       </c>
-      <c r="BO13" s="12" t="n">
+      <c r="BO13" s="10" t="n">
         <v>677</v>
       </c>
-      <c r="BP13" s="13">
+      <c r="BP13" s="11">
         <f>BO13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BQ13" s="12">
+        <f>BR13-BO13</f>
+        <v/>
+      </c>
+      <c r="BR13" s="12" t="n">
+        <v>684</v>
+      </c>
+      <c r="BS13" s="13">
+        <f>BR13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -3216,15 +3328,26 @@
         <f>BL14/$D$14</f>
         <v/>
       </c>
-      <c r="BN14" s="12">
+      <c r="BN14" s="10">
         <f>BO14-BL14</f>
         <v/>
       </c>
-      <c r="BO14" s="12" t="n">
+      <c r="BO14" s="10" t="n">
         <v>1173</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BP14" s="11">
         <f>BO14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BQ14" s="12">
+        <f>BR14-BO14</f>
+        <v/>
+      </c>
+      <c r="BR14" s="12" t="n">
+        <v>1179</v>
+      </c>
+      <c r="BS14" s="13">
+        <f>BR14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3469,15 +3592,26 @@
         <f>BL15/$D$15</f>
         <v/>
       </c>
-      <c r="BN15" s="12">
+      <c r="BN15" s="10">
         <f>BO15-BL15</f>
         <v/>
       </c>
-      <c r="BO15" s="12" t="n">
+      <c r="BO15" s="10" t="n">
         <v>149</v>
       </c>
-      <c r="BP15" s="13">
+      <c r="BP15" s="11">
         <f>BO15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BQ15" s="12">
+        <f>BR15-BO15</f>
+        <v/>
+      </c>
+      <c r="BR15" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="BS15" s="13">
+        <f>BR15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3658,15 +3792,26 @@
         <f>BL16/$D$16</f>
         <v/>
       </c>
-      <c r="BN16" s="12">
+      <c r="BN16" s="10">
         <f>BO16-BL16</f>
         <v/>
       </c>
-      <c r="BO16" s="12" t="n">
+      <c r="BO16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BP16" s="11">
         <f>BO16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BQ16" s="12">
+        <f>BR16-BO16</f>
+        <v/>
+      </c>
+      <c r="BR16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BS16" s="13">
+        <f>BR16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3748,9 +3893,12 @@
       <c r="BK17" s="10" t="n"/>
       <c r="BL17" s="10" t="n"/>
       <c r="BM17" s="11" t="n"/>
-      <c r="BN17" s="12" t="n"/>
-      <c r="BO17" s="12" t="n"/>
-      <c r="BP17" s="13" t="n"/>
+      <c r="BN17" s="10" t="n"/>
+      <c r="BO17" s="10" t="n"/>
+      <c r="BP17" s="11" t="n"/>
+      <c r="BQ17" s="12" t="n"/>
+      <c r="BR17" s="12" t="n"/>
+      <c r="BS17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3873,26 +4021,38 @@
         <f>BL18/$D$18</f>
         <v/>
       </c>
-      <c r="BN18" s="12">
+      <c r="BN18" s="10">
         <f>BO18-BL18</f>
         <v/>
       </c>
-      <c r="BO18" s="12" t="n">
+      <c r="BO18" s="10" t="n">
         <v>402</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BP18" s="11">
         <f>BO18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BQ18" s="12">
+        <f>BR18-BO18</f>
+        <v/>
+      </c>
+      <c r="BR18" s="12" t="n">
+        <v>440</v>
+      </c>
+      <c r="BS18" s="13">
+        <f>BR18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
